--- a/files/九龙-马头角-文曜.xlsx
+++ b/files/九龙-马头角-文曜.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文曜 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -609,7 +473,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -755,7 +619,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -801,7 +665,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -847,7 +711,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -893,7 +757,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -939,7 +803,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -985,7 +849,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1031,7 +895,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1077,7 +941,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1123,7 +987,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1169,7 +1033,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1215,7 +1079,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1261,7 +1125,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1357,7 +1221,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1403,7 +1267,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1449,7 +1313,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1495,7 +1359,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1541,7 +1405,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-31</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1587,7 +1451,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-29</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1633,7 +1497,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1679,7 +1543,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -1725,7 +1589,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1771,7 +1635,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1817,7 +1681,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1863,7 +1727,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1909,7 +1773,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1955,7 +1819,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2001,7 +1865,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2047,7 +1911,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2093,7 +1957,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2139,7 +2003,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2185,7 +2049,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2281,7 +2145,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-17</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2327,7 +2191,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2373,7 +2237,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-12</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2419,7 +2283,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2465,7 +2329,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-11</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2511,7 +2375,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2557,7 +2421,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2653,7 +2517,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2699,7 +2563,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-06-27</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2745,7 +2609,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-10</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2841,7 +2705,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2887,7 +2751,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2933,7 +2797,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-16</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2979,7 +2843,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3025,7 +2889,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3071,7 +2935,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3117,7 +2981,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3163,7 +3027,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3209,7 +3073,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3255,7 +3119,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-17</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3301,7 +3165,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-27</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3397,7 +3261,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3443,7 +3307,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3489,7 +3353,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-23</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3585,7 +3449,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3631,7 +3495,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3677,7 +3541,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3723,7 +3587,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-27</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3769,7 +3633,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3815,7 +3679,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3861,7 +3725,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3953,7 +3817,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3999,7 +3863,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4045,7 +3909,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4141,7 +4005,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4187,7 +4051,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-02</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4233,7 +4097,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4329,7 +4193,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4375,7 +4239,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-18</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4421,7 +4285,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4467,7 +4331,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4513,7 +4377,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4559,7 +4423,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4605,7 +4469,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4651,7 +4515,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4697,7 +4561,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4743,7 +4607,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4789,7 +4653,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4835,7 +4699,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4881,7 +4745,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4927,7 +4791,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-17</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4949,1035 +4813,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>文曜 - 文曜 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>92 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>82 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>9 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2183呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>A | 1046呎 (3房)
-$2,350万
-$22,467/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>B | 651呎 (2房)
-$1,321万
-$20,288/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$2,131万
-$23,572/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 634呎 (2房)
-$1,240万
-$19,552/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>B | 651呎 (2房)
-$1,310万
-$20,128/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$2,110万
-$23,338/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$748万
-$19,726/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 634呎 (2房)
-$1,230万
-$19,397/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>B | 651呎 (2房)
-$1,300万
-$19,968/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$2,077万
-$22,970/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$722万
-$19,037/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="inlineStr">
-        <is>
-          <t>A | 634呎 (2房)
-$1,225万
-$19,320/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>B | 651呎 (2房)
-$1,295万
-$19,888/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$719万
-$18,979/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="18" t="inlineStr">
-        <is>
-          <t>A | 634呎 (2房)
-$1,269万
-$20,013/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>B | 651呎 (2房)
-$1,290万
-$19,809/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$2,044万
-$22,607/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$771万
-$20,346/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,217万
-$19,166/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 650呎 (2房)
-$1,282万
-$19,730/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$1,931万
-$21,360/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$715万
-$18,867/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,212万
-$19,090/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 650呎 (2房)
-$1,377万
-$21,186/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$2,011万
-$22,250/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$734万
-$19,377/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,207万
-$19,013/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>B | 650呎 (2房)
-$1,272万
-$19,573/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$1,995万
-$22,073/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$711万
-$18,754/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,203万
-$18,938/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
-        <is>
-          <t>B | 650呎 (2房)
-$1,267万
-$19,495/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$709万
-$18,698/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,198万
-$18,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 650呎 (2房)
-$1,262万
-$19,417/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$1,870万
-$20,689/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$707万
-$18,643/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,198万
-$18,862/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 650呎 (2房)
-$1,325万
-$20,388/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$779万
-$20,566/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,188万
-$18,713/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,252万
-$19,293/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$702万
-$18,530/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,184万
-$18,639/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,247万
-$19,216/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>C | 905呎 (3房)
-$1,918万
-$21,189/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$700万
-$18,475/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,179万
-$18,565/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,242万
-$19,139/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>C | 905呎 (3房)
-$1,902万
-$21,021/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$698万
-$18,421/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,174万
-$18,490/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,299万
-$20,016/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 905呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$696万
-$18,364/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,169万
-$18,417/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,294万
-$19,936/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 905呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$687万
-$18,128/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,165万
-$18,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,289万
-$19,857/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 905呎 (3房)
-$1,857万
-$20,524/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$685万
-$18,073/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,160万
-$18,270/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,284万
-$19,778/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-$2,404万
-$26,594/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$683万
-$18,020/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,160万
-$18,270/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,284万
-$19,778/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$683万
-$18,020/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,151万
-$18,125/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,273万
-$19,621/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 904呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$679万
-$17,913/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,113万
-$17,528/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,173万
-$18,070/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 905呎 (2房)
-$1,730万
-$19,117/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$664万
-$17,509/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$1,137万
-$17,900/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,107万
-$17,060/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 905呎 (2房)
-$1,619万
-$17,892/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$626万
-$16,518/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>A | 635呎 (2房)
-$999万
-$15,730/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 649呎 (2房)
-$1,055万
-$16,254/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 856呎 (2房)
-$1,637万
-$19,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E29" s="18" t="inlineStr">
-        <is>
-          <t>D | 379呎 (1房)
-$599万
-$15,799/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-马头角-文曜.xlsx
+++ b/files/九龙-马头角-文曜.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文曜" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,95 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +141,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +222,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +652,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4813,4 +4991,1035 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>文曜 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2183呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 1046呎 (3房)
+$2350万
+$22,467/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>B | 651呎 (2房)
+$1321万
+$20,288/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$2131万
+$23,572/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 634呎 (2房)
+$1240万
+$19,552/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 651呎 (2房)
+$1310万
+$20,128/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$2110万
+$23,338/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$748万
+$19,726/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 634呎 (2房)
+$1230万
+$19,397/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>B | 651呎 (2房)
+$1300万
+$19,968/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$2077万
+$22,970/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$722万
+$19,037/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>A | 634呎 (2房)
+$1225万
+$19,320/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>B | 651呎 (2房)
+$1295万
+$19,888/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$719万
+$18,979/呎
+(24年-06月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 634呎 (2房)
+$1269万
+$20,013/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>B | 651呎 (2房)
+$1290万
+$19,809/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$2044万
+$22,607/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$771万
+$20,346/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1217万
+$19,166/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 650呎 (2房)
+$1282万
+$19,730/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$1931万
+$21,360/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$715万
+$18,867/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1212万
+$19,090/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 650呎 (2房)
+$1377万
+$21,186/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$2011万
+$22,250/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$734万
+$19,377/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1207万
+$19,013/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>B | 650呎 (2房)
+$1272万
+$19,573/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$1995万
+$22,073/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$711万
+$18,754/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1203万
+$18,938/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>B | 650呎 (2房)
+$1267万
+$19,495/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$709万
+$18,698/呎
+(24年-04月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1198万
+$18,862/呎
+(24年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 650呎 (2房)
+$1262万
+$19,417/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$1870万
+$20,689/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$707万
+$18,643/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1198万
+$18,862/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 650呎 (2房)
+$1325万
+$20,388/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$779万
+$20,566/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1188万
+$18,713/呎
+(24年-04月)</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1252万
+$19,293/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$702万
+$18,530/呎
+(24年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1184万
+$18,639/呎
+(23年-11月)</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1247万
+$19,216/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>C | 905呎 (3房)
+$1918万
+$21,189/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$700万
+$18,475/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1179万
+$18,565/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1242万
+$19,139/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>C | 905呎 (3房)
+$1902万
+$21,021/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$698万
+$18,421/呎
+(24年-05月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1174万
+$18,490/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1299万
+$20,016/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 905呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$696万
+$18,364/呎
+(23年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1169万
+$18,417/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1294万
+$19,936/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 905呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$687万
+$18,128/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1165万
+$18,344/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1289万
+$19,857/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 905呎 (3房)
+$1857万
+$20,524/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$685万
+$18,073/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1160万
+$18,270/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1284万
+$19,778/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+$2404万
+$26,594/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$683万
+$18,020/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1160万
+$18,270/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1284万
+$19,778/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$683万
+$18,020/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1151万
+$18,125/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1273万
+$19,621/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 904呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$679万
+$17,913/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1113万
+$17,528/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1173万
+$18,070/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 905呎 (2房)
+$1730万
+$19,117/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$664万
+$17,509/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$1137万
+$17,900/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1107万
+$17,060/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 905呎 (2房)
+$1619万
+$17,892/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$626万
+$16,518/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>A | 635呎 (2房)
+$999万
+$15,730/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 649呎 (2房)
+$1055万
+$16,254/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 856呎 (2房)
+$1637万
+$19,129/呎
+(23年-10月)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>D | 379呎 (1房)
+$599万
+$15,799/呎
+(23年-10月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-马头角-文曜.xlsx
+++ b/files/九龙-马头角-文曜.xlsx
@@ -652,7 +652,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-马头角-文曜.xlsx
+++ b/files/九龙-马头角-文曜.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -655,6 +655,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -712,6 +716,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -762,6 +786,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -808,6 +852,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>21308700</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>23572</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -854,6 +914,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>13207500</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>20288</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -900,6 +976,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>23500000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>22467</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -946,6 +1038,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>7476000</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>19726</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -992,6 +1100,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>21097100</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>23338</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1038,6 +1162,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>13103200</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>20128</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1084,6 +1224,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>12396000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>19552</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1130,6 +1286,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>7215000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>19037</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1176,6 +1348,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>20765200</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>22970</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1222,6 +1410,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>12999000</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>19968</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1268,6 +1472,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>12297700</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>19397</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1314,6 +1534,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>7193200</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>18979</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1364,6 +1600,26 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1410,6 +1666,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>12947200</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>19888</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1456,6 +1728,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>12249000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>19320</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1502,6 +1790,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>7711200</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>20346</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1548,6 +1852,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>20437100</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>22607</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1594,6 +1914,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>12895500</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>19809</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1640,6 +1976,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>12688200</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>20013</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1686,6 +2038,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>7150500</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>18867</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1732,6 +2100,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>19309200</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>21360</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1778,6 +2162,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>12824200</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>19730</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1824,6 +2224,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>12170200</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>19166</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1870,6 +2286,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>7344000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>19377</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1916,6 +2348,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>20113700</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>22250</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1962,6 +2410,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>13770900</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>21186</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2008,6 +2472,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>12122200</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>19090</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2054,6 +2534,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>7107700</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>18754</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2100,6 +2596,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>19954200</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>22073</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2146,6 +2658,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>12722200</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>19573</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2192,6 +2720,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>12073500</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>19013</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2238,6 +2782,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>7086700</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>18698</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2288,6 +2848,26 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2334,6 +2914,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>12672000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>19495</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2380,6 +2976,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>12025500</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>18938</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2426,6 +3038,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>7065700</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>18643</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2472,6 +3100,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>18703300</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>20689</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2518,6 +3162,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>12621000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>19417</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2564,6 +3224,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>11977500</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>18862</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2610,6 +3286,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>7794700</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>20566</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2660,6 +3352,26 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2706,6 +3418,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>13252000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>20388</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2752,6 +3480,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>11977500</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>18862</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2798,6 +3542,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>7023000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>18530</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2848,6 +3608,26 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2894,6 +3674,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>12521200</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>19293</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2940,6 +3736,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>11883000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>18713</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2986,6 +3798,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>7002000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>18475</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3032,6 +3860,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>19176200</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>21189</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3078,6 +3922,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>12471000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>19216</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3124,6 +3984,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>11835700</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>18639</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3170,6 +4046,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>6981700</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>18421</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3216,6 +4108,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>19023700</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>21021</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3262,6 +4170,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>12421500</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>19139</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3308,6 +4232,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>11788500</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>18565</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3354,6 +4294,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>6960000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>18364</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3404,6 +4360,26 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3450,6 +4426,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>12990600</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>20016</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3496,6 +4488,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>11741200</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>18490</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3542,6 +4550,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>6870700</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>18128</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3592,6 +4616,26 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3638,6 +4682,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>12938600</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>19936</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3684,6 +4744,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>11694700</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>18417</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3730,6 +4806,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>6849700</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>18073</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3776,6 +4868,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>18574500</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>20524</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3822,6 +4930,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>12887400</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>19857</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3868,6 +4992,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>11648200</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>18344</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3914,6 +5054,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>6829500</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>18020</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3960,6 +5116,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>26%</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>17790340</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>19680</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>換樓易建期付款</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4006,6 +5178,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>12836200</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>19778</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4052,6 +5240,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>11601700</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>18270</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4098,6 +5302,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>6829500</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>18020</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4148,6 +5368,26 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4194,6 +5434,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>12836200</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>19778</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4240,6 +5496,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>11601700</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>18270</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4286,6 +5558,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>6789000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>17913</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4336,6 +5624,26 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4382,6 +5690,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>12733800</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>19621</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4428,6 +5752,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>11509500</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>18125</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4474,6 +5814,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>6636000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>17509</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4520,6 +5876,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>17300600</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>19117</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4566,6 +5938,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>11727700</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>18070</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4612,6 +6000,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>11130000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>17528</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4658,6 +6062,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>6260200</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>16518</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4704,6 +6124,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>16192300</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>17892</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4750,6 +6186,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>11072200</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>17060</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4796,6 +6248,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>11366500</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>17900</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4842,6 +6310,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>5988000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>15799</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4888,6 +6372,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>16374600</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>19129</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4934,6 +6434,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>10548700</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>16254</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4980,13 +6496,29 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>9988500</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>15730</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -5136,7 +6668,7 @@
           <t>A | 1046呎 (3房)
 $2350万
 $22,467/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -5144,7 +6676,7 @@
           <t>B | 651呎 (2房)
 $1321万
 $20,288/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -5152,7 +6684,7 @@
           <t>C | 904呎 (3房)
 $2131万
 $23,572/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -5168,7 +6700,7 @@
           <t>A | 634呎 (2房)
 $1240万
 $19,552/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -5176,7 +6708,7 @@
           <t>B | 651呎 (2房)
 $1310万
 $20,128/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -5184,7 +6716,7 @@
           <t>C | 904呎 (3房)
 $2110万
 $23,338/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -5192,7 +6724,7 @@
           <t>D | 379呎 (1房)
 $748万
 $19,726/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -5207,7 +6739,7 @@
           <t>A | 634呎 (2房)
 $1230万
 $19,397/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -5215,7 +6747,7 @@
           <t>B | 651呎 (2房)
 $1300万
 $19,968/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -5223,7 +6755,7 @@
           <t>C | 904呎 (3房)
 $2077万
 $22,970/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -5231,7 +6763,7 @@
           <t>D | 379呎 (1房)
 $722万
 $19,037/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -5246,7 +6778,7 @@
           <t>A | 634呎 (2房)
 $1225万
 $19,320/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -5254,7 +6786,7 @@
           <t>B | 651呎 (2房)
 $1295万
 $19,888/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -5270,7 +6802,7 @@
           <t>D | 379呎 (1房)
 $719万
 $18,979/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -5285,7 +6817,7 @@
           <t>A | 634呎 (2房)
 $1269万
 $20,013/呎
-(23年-10月)</t>
+(23年-10月-29日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -5293,7 +6825,7 @@
           <t>B | 651呎 (2房)
 $1290万
 $19,809/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -5301,7 +6833,7 @@
           <t>C | 904呎 (3房)
 $2044万
 $22,607/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -5309,7 +6841,7 @@
           <t>D | 379呎 (1房)
 $771万
 $20,346/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -5324,7 +6856,7 @@
           <t>A | 635呎 (2房)
 $1217万
 $19,166/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -5332,7 +6864,7 @@
           <t>B | 650呎 (2房)
 $1282万
 $19,730/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -5340,7 +6872,7 @@
           <t>C | 904呎 (3房)
 $1931万
 $21,360/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -5348,7 +6880,7 @@
           <t>D | 379呎 (1房)
 $715万
 $18,867/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -5363,7 +6895,7 @@
           <t>A | 635呎 (2房)
 $1212万
 $19,090/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -5371,7 +6903,7 @@
           <t>B | 650呎 (2房)
 $1377万
 $21,186/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -5379,7 +6911,7 @@
           <t>C | 904呎 (3房)
 $2011万
 $22,250/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -5387,7 +6919,7 @@
           <t>D | 379呎 (1房)
 $734万
 $19,377/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -5402,7 +6934,7 @@
           <t>A | 635呎 (2房)
 $1207万
 $19,013/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -5410,7 +6942,7 @@
           <t>B | 650呎 (2房)
 $1272万
 $19,573/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -5418,7 +6950,7 @@
           <t>C | 904呎 (3房)
 $1995万
 $22,073/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -5426,7 +6958,7 @@
           <t>D | 379呎 (1房)
 $711万
 $18,754/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -5441,7 +6973,7 @@
           <t>A | 635呎 (2房)
 $1203万
 $18,938/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -5449,7 +6981,7 @@
           <t>B | 650呎 (2房)
 $1267万
 $19,495/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -5465,7 +6997,7 @@
           <t>D | 379呎 (1房)
 $709万
 $18,698/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -5480,7 +7012,7 @@
           <t>A | 635呎 (2房)
 $1198万
 $18,862/呎
-(24年-03月)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -5488,7 +7020,7 @@
           <t>B | 650呎 (2房)
 $1262万
 $19,417/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -5496,7 +7028,7 @@
           <t>C | 904呎 (3房)
 $1870万
 $20,689/呎
-(23年-10月)</t>
+(23年-10月-26日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -5504,7 +7036,7 @@
           <t>D | 379呎 (1房)
 $707万
 $18,643/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -5519,7 +7051,7 @@
           <t>A | 635呎 (2房)
 $1198万
 $18,862/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -5527,7 +7059,7 @@
           <t>B | 650呎 (2房)
 $1325万
 $20,388/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -5543,7 +7075,7 @@
           <t>D | 379呎 (1房)
 $779万
 $20,566/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -5558,7 +7090,7 @@
           <t>A | 635呎 (2房)
 $1188万
 $18,713/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -5566,7 +7098,7 @@
           <t>B | 649呎 (2房)
 $1252万
 $19,293/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -5582,7 +7114,7 @@
           <t>D | 379呎 (1房)
 $702万
 $18,530/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -5597,7 +7129,7 @@
           <t>A | 635呎 (2房)
 $1184万
 $18,639/呎
-(23年-11月)</t>
+(23年-11月-12日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -5605,7 +7137,7 @@
           <t>B | 649呎 (2房)
 $1247万
 $19,216/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -5613,7 +7145,7 @@
           <t>C | 905呎 (3房)
 $1918万
 $21,189/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -5621,7 +7153,7 @@
           <t>D | 379呎 (1房)
 $700万
 $18,475/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -5636,7 +7168,7 @@
           <t>A | 635呎 (2房)
 $1179万
 $18,565/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -5644,7 +7176,7 @@
           <t>B | 649呎 (2房)
 $1242万
 $19,139/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -5652,7 +7184,7 @@
           <t>C | 905呎 (3房)
 $1902万
 $21,021/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -5660,7 +7192,7 @@
           <t>D | 379呎 (1房)
 $698万
 $18,421/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -5675,7 +7207,7 @@
           <t>A | 635呎 (2房)
 $1174万
 $18,490/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -5683,7 +7215,7 @@
           <t>B | 649呎 (2房)
 $1299万
 $20,016/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -5699,7 +7231,7 @@
           <t>D | 379呎 (1房)
 $696万
 $18,364/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -5714,7 +7246,7 @@
           <t>A | 635呎 (2房)
 $1169万
 $18,417/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -5722,7 +7254,7 @@
           <t>B | 649呎 (2房)
 $1294万
 $19,936/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -5738,7 +7270,7 @@
           <t>D | 379呎 (1房)
 $687万
 $18,128/呎
-(23年-10月)</t>
+(23年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -5753,7 +7285,7 @@
           <t>A | 635呎 (2房)
 $1165万
 $18,344/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -5761,7 +7293,7 @@
           <t>B | 649呎 (2房)
 $1289万
 $19,857/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -5769,7 +7301,7 @@
           <t>C | 905呎 (3房)
 $1857万
 $20,524/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -5777,7 +7309,7 @@
           <t>D | 379呎 (1房)
 $685万
 $18,073/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -5792,7 +7324,7 @@
           <t>A | 635呎 (2房)
 $1160万
 $18,270/呎
-(23年-10月)</t>
+(23年-10月-15日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -5800,7 +7332,7 @@
           <t>B | 649呎 (2房)
 $1284万
 $19,778/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -5816,7 +7348,7 @@
           <t>D | 379呎 (1房)
 $683万
 $18,020/呎
-(23年-10月)</t>
+(23年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -5831,7 +7363,7 @@
           <t>A | 635呎 (2房)
 $1160万
 $18,270/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -5839,7 +7371,7 @@
           <t>B | 649呎 (2房)
 $1284万
 $19,778/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -5855,7 +7387,7 @@
           <t>D | 379呎 (1房)
 $683万
 $18,020/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -5870,7 +7402,7 @@
           <t>A | 635呎 (2房)
 $1151万
 $18,125/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -5878,7 +7410,7 @@
           <t>B | 649呎 (2房)
 $1273万
 $19,621/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -5894,7 +7426,7 @@
           <t>D | 379呎 (1房)
 $679万
 $17,913/呎
-(23年-10月)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -5909,7 +7441,7 @@
           <t>A | 635呎 (2房)
 $1113万
 $17,528/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -5917,7 +7449,7 @@
           <t>B | 649呎 (2房)
 $1173万
 $18,070/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -5925,7 +7457,7 @@
           <t>C | 905呎 (2房)
 $1730万
 $19,117/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -5933,7 +7465,7 @@
           <t>D | 379呎 (1房)
 $664万
 $17,509/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -5948,7 +7480,7 @@
           <t>A | 635呎 (2房)
 $1137万
 $17,900/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -5956,7 +7488,7 @@
           <t>B | 649呎 (2房)
 $1107万
 $17,060/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -5964,7 +7496,7 @@
           <t>C | 905呎 (2房)
 $1619万
 $17,892/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -5972,7 +7504,7 @@
           <t>D | 379呎 (1房)
 $626万
 $16,518/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -5987,7 +7519,7 @@
           <t>A | 635呎 (2房)
 $999万
 $15,730/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -5995,7 +7527,7 @@
           <t>B | 649呎 (2房)
 $1055万
 $16,254/呎
-(23年-10月)</t>
+(23年-10月-25日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -6003,7 +7535,7 @@
           <t>C | 856呎 (2房)
 $1637万
 $19,129/呎
-(23年-10月)</t>
+(23年-10月-30日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -6011,7 +7543,7 @@
           <t>D | 379呎 (1房)
 $599万
 $15,799/呎
-(23年-10月)</t>
+(23年-10月-15日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-文曜.xlsx
+++ b/files/九龙-马头角-文曜.xlsx
@@ -6668,7 +6668,7 @@
           <t>A | 1046呎 (3房)
 $2350万
 $22,467/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6676,7 +6676,7 @@
           <t>B | 651呎 (2房)
 $1321万
 $20,288/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -6684,7 +6684,7 @@
           <t>C | 904呎 (3房)
 $2131万
 $23,572/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -6700,7 +6700,7 @@
           <t>A | 634呎 (2房)
 $1240万
 $19,552/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6708,7 +6708,7 @@
           <t>B | 651呎 (2房)
 $1310万
 $20,128/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6716,7 +6716,7 @@
           <t>C | 904呎 (3房)
 $2110万
 $23,338/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6724,7 +6724,7 @@
           <t>D | 379呎 (1房)
 $748万
 $19,726/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
           <t>A | 634呎 (2房)
 $1230万
 $19,397/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -6747,7 +6747,7 @@
           <t>B | 651呎 (2房)
 $1300万
 $19,968/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -6755,7 +6755,7 @@
           <t>C | 904呎 (3房)
 $2077万
 $22,970/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6763,7 +6763,7 @@
           <t>D | 379呎 (1房)
 $722万
 $19,037/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
           <t>A | 634呎 (2房)
 $1225万
 $19,320/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6786,7 +6786,7 @@
           <t>B | 651呎 (2房)
 $1295万
 $19,888/呎
-(26年-03月-08日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6802,7 +6802,7 @@
           <t>D | 379呎 (1房)
 $719万
 $18,979/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
           <t>A | 634呎 (2房)
 $1269万
 $20,013/呎
-(23年-10月-29日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6825,7 +6825,7 @@
           <t>B | 651呎 (2房)
 $1290万
 $19,809/呎
-(25年-08月-31日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6833,7 +6833,7 @@
           <t>C | 904呎 (3房)
 $2044万
 $22,607/呎
-(25年-06月-17日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6841,7 +6841,7 @@
           <t>D | 379呎 (1房)
 $771万
 $20,346/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
           <t>A | 635呎 (2房)
 $1217万
 $19,166/呎
-(23年-10月-16日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6864,7 +6864,7 @@
           <t>B | 650呎 (2房)
 $1282万
 $19,730/呎
-(24年-12月-05日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6872,7 +6872,7 @@
           <t>C | 904呎 (3房)
 $1931万
 $21,360/呎
-(23年-10月-19日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6880,7 +6880,7 @@
           <t>D | 379呎 (1房)
 $715万
 $18,867/呎
-(23年-10月-17日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
           <t>A | 635呎 (2房)
 $1212万
 $19,090/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6903,7 +6903,7 @@
           <t>B | 650呎 (2房)
 $1377万
 $21,186/呎
-(26年-06月-21日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6911,7 +6911,7 @@
           <t>C | 904呎 (3房)
 $2011万
 $22,250/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6919,7 +6919,7 @@
           <t>D | 379呎 (1房)
 $734万
 $19,377/呎
-(25年-07月-07日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
           <t>A | 635呎 (2房)
 $1207万
 $19,013/呎
-(23年-10月-16日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6942,7 +6942,7 @@
           <t>B | 650呎 (2房)
 $1272万
 $19,573/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6950,7 +6950,7 @@
           <t>C | 904呎 (3房)
 $1995万
 $22,073/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6958,7 +6958,7 @@
           <t>D | 379呎 (1房)
 $711万
 $18,754/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
           <t>A | 635呎 (2房)
 $1203万
 $18,938/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -6981,7 +6981,7 @@
           <t>B | 650呎 (2房)
 $1267万
 $19,495/呎
-(25年-08月-17日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6997,7 +6997,7 @@
           <t>D | 379呎 (1房)
 $709万
 $18,698/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
           <t>A | 635呎 (2房)
 $1198万
 $18,862/呎
-(24年-03月-18日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7020,7 +7020,7 @@
           <t>B | 650呎 (2房)
 $1262万
 $19,417/呎
-(24年-12月-11日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -7028,7 +7028,7 @@
           <t>C | 904呎 (3房)
 $1870万
 $20,689/呎
-(23年-10月-26日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -7036,7 +7036,7 @@
           <t>D | 379呎 (1房)
 $707万
 $18,643/呎
-(24年-12月-12日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
           <t>A | 635呎 (2房)
 $1198万
 $18,862/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7059,7 +7059,7 @@
           <t>B | 650呎 (2房)
 $1325万
 $20,388/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -7075,7 +7075,7 @@
           <t>D | 379呎 (1房)
 $779万
 $20,566/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
           <t>A | 635呎 (2房)
 $1188万
 $18,713/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7098,7 +7098,7 @@
           <t>B | 649呎 (2房)
 $1252万
 $19,293/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -7114,7 +7114,7 @@
           <t>D | 379呎 (1房)
 $702万
 $18,530/呎
-(24年-12月-10日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
           <t>A | 635呎 (2房)
 $1184万
 $18,639/呎
-(23年-11月-12日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7137,7 +7137,7 @@
           <t>B | 649呎 (2房)
 $1247万
 $19,216/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7145,7 +7145,7 @@
           <t>C | 905呎 (3房)
 $1918万
 $21,189/呎
-(25年-06月-04日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7153,7 +7153,7 @@
           <t>D | 379呎 (1房)
 $700万
 $18,475/呎
-(23年-10月-16日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
           <t>A | 635呎 (2房)
 $1179万
 $18,565/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7176,7 +7176,7 @@
           <t>B | 649呎 (2房)
 $1242万
 $19,139/呎
-(26年-03月-02日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7184,7 +7184,7 @@
           <t>C | 905呎 (3房)
 $1902万
 $21,021/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -7192,7 +7192,7 @@
           <t>D | 379呎 (1房)
 $698万
 $18,421/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
           <t>A | 635呎 (2房)
 $1174万
 $18,490/呎
-(24年-11月-19日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7215,7 +7215,7 @@
           <t>B | 649呎 (2房)
 $1299万
 $20,016/呎
-(26年-05月-31日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -7231,7 +7231,7 @@
           <t>D | 379呎 (1房)
 $696万
 $18,364/呎
-(23年-11月-27日)</t>
+(23年-11月)</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
           <t>A | 635呎 (2房)
 $1169万
 $18,417/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7254,7 +7254,7 @@
           <t>B | 649呎 (2房)
 $1294万
 $19,936/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -7270,7 +7270,7 @@
           <t>D | 379呎 (1房)
 $687万
 $18,128/呎
-(23年-10月-23日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
           <t>A | 635呎 (2房)
 $1165万
 $18,344/呎
-(24年-11月-10日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -7293,7 +7293,7 @@
           <t>B | 649呎 (2房)
 $1289万
 $19,857/呎
-(26年-06月-02日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -7301,7 +7301,7 @@
           <t>C | 905呎 (3房)
 $1857万
 $20,524/呎
-(25年-01月-27日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7309,7 +7309,7 @@
           <t>D | 379呎 (1房)
 $685万
 $18,073/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
           <t>A | 635呎 (2房)
 $1160万
 $18,270/呎
-(23年-10月-15日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -7332,7 +7332,7 @@
           <t>B | 649呎 (2房)
 $1284万
 $19,778/呎
-(26年-06月-04日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -7348,7 +7348,7 @@
           <t>D | 379呎 (1房)
 $683万
 $18,020/呎
-(23年-10月-15日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
           <t>A | 635呎 (2房)
 $1160万
 $18,270/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -7371,7 +7371,7 @@
           <t>B | 649呎 (2房)
 $1284万
 $19,778/呎
-(26年-06月-11日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -7387,7 +7387,7 @@
           <t>D | 379呎 (1房)
 $683万
 $18,020/呎
-(23年-10月-19日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
           <t>A | 635呎 (2房)
 $1151万
 $18,125/呎
-(23年-10月-18日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -7410,7 +7410,7 @@
           <t>B | 649呎 (2房)
 $1273万
 $19,621/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -7426,7 +7426,7 @@
           <t>D | 379呎 (1房)
 $679万
 $17,913/呎
-(23年-10月-24日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
           <t>A | 635呎 (2房)
 $1113万
 $17,528/呎
-(23年-10月-17日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -7449,7 +7449,7 @@
           <t>B | 649呎 (2房)
 $1173万
 $18,070/呎
-(25年-10月-23日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -7457,7 +7457,7 @@
           <t>C | 905呎 (2房)
 $1730万
 $19,117/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -7465,7 +7465,7 @@
           <t>D | 379呎 (1房)
 $664万
 $17,509/呎
-(23年-10月-17日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
           <t>A | 635呎 (2房)
 $1137万
 $17,900/呎
-(25年-11月-13日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -7488,7 +7488,7 @@
           <t>B | 649呎 (2房)
 $1107万
 $17,060/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -7496,7 +7496,7 @@
           <t>C | 905呎 (2房)
 $1619万
 $17,892/呎
-(25年-11月-02日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -7504,7 +7504,7 @@
           <t>D | 379呎 (1房)
 $626万
 $16,518/呎
-(23年-10月-17日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
           <t>A | 635呎 (2房)
 $999万
 $15,730/呎
-(23年-10月-17日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -7527,7 +7527,7 @@
           <t>B | 649呎 (2房)
 $1055万
 $16,254/呎
-(23年-10月-25日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -7535,7 +7535,7 @@
           <t>C | 856呎 (2房)
 $1637万
 $19,129/呎
-(23年-10月-30日)</t>
+(23年-10月)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -7543,7 +7543,7 @@
           <t>D | 379呎 (1房)
 $599万
 $15,799/呎
-(23年-10月-15日)</t>
+(23年-10月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-文曜.xlsx
+++ b/files/九龙-马头角-文曜.xlsx
@@ -6668,7 +6668,7 @@
           <t>A | 1046呎 (3房)
 $2350万
 $22,467/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -6676,7 +6676,7 @@
           <t>B | 651呎 (2房)
 $1321万
 $20,288/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -6684,7 +6684,7 @@
           <t>C | 904呎 (3房)
 $2131万
 $23,572/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr"/>
@@ -6700,7 +6700,7 @@
           <t>A | 634呎 (2房)
 $1240万
 $19,552/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -6708,7 +6708,7 @@
           <t>B | 651呎 (2房)
 $1310万
 $20,128/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -6716,7 +6716,7 @@
           <t>C | 904呎 (3房)
 $2110万
 $23,338/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -6724,7 +6724,7 @@
           <t>D | 379呎 (1房)
 $748万
 $19,726/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
           <t>A | 634呎 (2房)
 $1230万
 $19,397/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -6747,7 +6747,7 @@
           <t>B | 651呎 (2房)
 $1300万
 $19,968/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -6755,7 +6755,7 @@
           <t>C | 904呎 (3房)
 $2077万
 $22,970/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -6763,7 +6763,7 @@
           <t>D | 379呎 (1房)
 $722万
 $19,037/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
           <t>A | 634呎 (2房)
 $1225万
 $19,320/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6786,7 +6786,7 @@
           <t>B | 651呎 (2房)
 $1295万
 $19,888/呎
-(26年-03月)</t>
+(26年-03月-08日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -6802,7 +6802,7 @@
           <t>D | 379呎 (1房)
 $719万
 $18,979/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6817,7 @@
           <t>A | 634呎 (2房)
 $1269万
 $20,013/呎
-(23年-10月)</t>
+(23年-10月-29日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6825,7 +6825,7 @@
           <t>B | 651呎 (2房)
 $1290万
 $19,809/呎
-(25年-08月)</t>
+(25年-08月-31日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6833,7 +6833,7 @@
           <t>C | 904呎 (3房)
 $2044万
 $22,607/呎
-(25年-06月)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6841,7 +6841,7 @@
           <t>D | 379呎 (1房)
 $771万
 $20,346/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
           <t>A | 635呎 (2房)
 $1217万
 $19,166/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6864,7 +6864,7 @@
           <t>B | 650呎 (2房)
 $1282万
 $19,730/呎
-(24年-12月)</t>
+(24年-12月-05日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6872,7 +6872,7 @@
           <t>C | 904呎 (3房)
 $1931万
 $21,360/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6880,7 +6880,7 @@
           <t>D | 379呎 (1房)
 $715万
 $18,867/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
           <t>A | 635呎 (2房)
 $1212万
 $19,090/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6903,7 +6903,7 @@
           <t>B | 650呎 (2房)
 $1377万
 $21,186/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6911,7 +6911,7 @@
           <t>C | 904呎 (3房)
 $2011万
 $22,250/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6919,7 +6919,7 @@
           <t>D | 379呎 (1房)
 $734万
 $19,377/呎
-(25年-07月)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
           <t>A | 635呎 (2房)
 $1207万
 $19,013/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6942,7 +6942,7 @@
           <t>B | 650呎 (2房)
 $1272万
 $19,573/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6950,7 +6950,7 @@
           <t>C | 904呎 (3房)
 $1995万
 $22,073/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6958,7 +6958,7 @@
           <t>D | 379呎 (1房)
 $711万
 $18,754/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -6973,7 +6973,7 @@
           <t>A | 635呎 (2房)
 $1203万
 $18,938/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -6981,7 +6981,7 @@
           <t>B | 650呎 (2房)
 $1267万
 $19,495/呎
-(25年-08月)</t>
+(25年-08月-17日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -6997,7 +6997,7 @@
           <t>D | 379呎 (1房)
 $709万
 $18,698/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -7012,7 +7012,7 @@
           <t>A | 635呎 (2房)
 $1198万
 $18,862/呎
-(24年-03月)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -7020,7 +7020,7 @@
           <t>B | 650呎 (2房)
 $1262万
 $19,417/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -7028,7 +7028,7 @@
           <t>C | 904呎 (3房)
 $1870万
 $20,689/呎
-(23年-10月)</t>
+(23年-10月-26日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -7036,7 +7036,7 @@
           <t>D | 379呎 (1房)
 $707万
 $18,643/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7051,7 @@
           <t>A | 635呎 (2房)
 $1198万
 $18,862/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -7059,7 +7059,7 @@
           <t>B | 650呎 (2房)
 $1325万
 $20,388/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -7075,7 +7075,7 @@
           <t>D | 379呎 (1房)
 $779万
 $20,566/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
           <t>A | 635呎 (2房)
 $1188万
 $18,713/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -7098,7 +7098,7 @@
           <t>B | 649呎 (2房)
 $1252万
 $19,293/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -7114,7 +7114,7 @@
           <t>D | 379呎 (1房)
 $702万
 $18,530/呎
-(24年-12月)</t>
+(24年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
           <t>A | 635呎 (2房)
 $1184万
 $18,639/呎
-(23年-11月)</t>
+(23年-11月-12日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7137,7 +7137,7 @@
           <t>B | 649呎 (2房)
 $1247万
 $19,216/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -7145,7 +7145,7 @@
           <t>C | 905呎 (3房)
 $1918万
 $21,189/呎
-(25年-06月)</t>
+(25年-06月-04日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -7153,7 +7153,7 @@
           <t>D | 379呎 (1房)
 $700万
 $18,475/呎
-(23年-10月)</t>
+(23年-10月-16日)</t>
         </is>
       </c>
     </row>
@@ -7168,7 +7168,7 @@
           <t>A | 635呎 (2房)
 $1179万
 $18,565/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7176,7 +7176,7 @@
           <t>B | 649呎 (2房)
 $1242万
 $19,139/呎
-(26年-03月)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7184,7 +7184,7 @@
           <t>C | 905呎 (3房)
 $1902万
 $21,021/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -7192,7 +7192,7 @@
           <t>D | 379呎 (1房)
 $698万
 $18,421/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -7207,7 +7207,7 @@
           <t>A | 635呎 (2房)
 $1174万
 $18,490/呎
-(24年-11月)</t>
+(24年-11月-19日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7215,7 +7215,7 @@
           <t>B | 649呎 (2房)
 $1299万
 $20,016/呎
-(26年-05月)</t>
+(26年-05月-31日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -7231,7 +7231,7 @@
           <t>D | 379呎 (1房)
 $696万
 $18,364/呎
-(23年-11月)</t>
+(23年-11月-27日)</t>
         </is>
       </c>
     </row>
@@ -7246,7 +7246,7 @@
           <t>A | 635呎 (2房)
 $1169万
 $18,417/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7254,7 +7254,7 @@
           <t>B | 649呎 (2房)
 $1294万
 $19,936/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -7270,7 +7270,7 @@
           <t>D | 379呎 (1房)
 $687万
 $18,128/呎
-(23年-10月)</t>
+(23年-10月-23日)</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
           <t>A | 635呎 (2房)
 $1165万
 $18,344/呎
-(24年-11月)</t>
+(24年-11月-10日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -7293,7 +7293,7 @@
           <t>B | 649呎 (2房)
 $1289万
 $19,857/呎
-(26年-06月)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -7301,7 +7301,7 @@
           <t>C | 905呎 (3房)
 $1857万
 $20,524/呎
-(25年-01月)</t>
+(25年-01月-27日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -7309,7 +7309,7 @@
           <t>D | 379呎 (1房)
 $685万
 $18,073/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7324,7 @@
           <t>A | 635呎 (2房)
 $1160万
 $18,270/呎
-(23年-10月)</t>
+(23年-10月-15日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -7332,7 +7332,7 @@
           <t>B | 649呎 (2房)
 $1284万
 $19,778/呎
-(26年-06月)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -7348,7 +7348,7 @@
           <t>D | 379呎 (1房)
 $683万
 $18,020/呎
-(23年-10月)</t>
+(23年-10月-15日)</t>
         </is>
       </c>
     </row>
@@ -7363,7 +7363,7 @@
           <t>A | 635呎 (2房)
 $1160万
 $18,270/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -7371,7 +7371,7 @@
           <t>B | 649呎 (2房)
 $1284万
 $19,778/呎
-(26年-06月)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -7387,7 +7387,7 @@
           <t>D | 379呎 (1房)
 $683万
 $18,020/呎
-(23年-10月)</t>
+(23年-10月-19日)</t>
         </is>
       </c>
     </row>
@@ -7402,7 +7402,7 @@
           <t>A | 635呎 (2房)
 $1151万
 $18,125/呎
-(23年-10月)</t>
+(23年-10月-18日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -7410,7 +7410,7 @@
           <t>B | 649呎 (2房)
 $1273万
 $19,621/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -7426,7 +7426,7 @@
           <t>D | 379呎 (1房)
 $679万
 $17,913/呎
-(23年-10月)</t>
+(23年-10月-24日)</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
           <t>A | 635呎 (2房)
 $1113万
 $17,528/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -7449,7 +7449,7 @@
           <t>B | 649呎 (2房)
 $1173万
 $18,070/呎
-(25年-10月)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -7457,7 +7457,7 @@
           <t>C | 905呎 (2房)
 $1730万
 $19,117/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -7465,7 +7465,7 @@
           <t>D | 379呎 (1房)
 $664万
 $17,509/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -7480,7 +7480,7 @@
           <t>A | 635呎 (2房)
 $1137万
 $17,900/呎
-(25年-11月)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -7488,7 +7488,7 @@
           <t>B | 649呎 (2房)
 $1107万
 $17,060/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -7496,7 +7496,7 @@
           <t>C | 905呎 (2房)
 $1619万
 $17,892/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -7504,7 +7504,7 @@
           <t>D | 379呎 (1房)
 $626万
 $16,518/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
           <t>A | 635呎 (2房)
 $999万
 $15,730/呎
-(23年-10月)</t>
+(23年-10月-17日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -7527,7 +7527,7 @@
           <t>B | 649呎 (2房)
 $1055万
 $16,254/呎
-(23年-10月)</t>
+(23年-10月-25日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -7535,7 +7535,7 @@
           <t>C | 856呎 (2房)
 $1637万
 $19,129/呎
-(23年-10月)</t>
+(23年-10月-30日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -7543,7 +7543,7 @@
           <t>D | 379呎 (1房)
 $599万
 $15,799/呎
-(23年-10月)</t>
+(23年-10月-15日)</t>
         </is>
       </c>
     </row>
